--- a/signup_forms/024_wordpress_website_maintenance_subscription_signup--signup_forms.xlsx
+++ b/signup_forms/024_wordpress_website_maintenance_subscription_signup--signup_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C48"/>
+  <dimension ref="A1:C47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1517,17 +1517,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>contact_method_choices</t>
+          <t>website_type_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>wordpress</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>WordPress</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>wordpress</t>
+          <t>html</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>WordPress</t>
+          <t>HTML</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>html</t>
+          <t>php</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>HTML</t>
+          <t>PHP</t>
         </is>
       </c>
     </row>
@@ -1573,29 +1573,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>php</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>PHP</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>website_type_choices</t>
+          <t>subscription_status_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>trial</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Trial</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>trial</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Trial</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
@@ -1641,29 +1641,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>inactive</t>
+          <t>expired</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>Expired</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>subscription_status_choices</t>
+          <t>payment_frequency_2_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>expired</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Expired</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Weekly</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1692,29 +1692,29 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annually</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Annually</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>payment_frequency_2_choices</t>
+          <t>custom_plan_duration_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>annually</t>
+          <t>1_month</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Annually</t>
+          <t>1 Month</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1_month</t>
+          <t>3_months</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1 Month</t>
+          <t>3 Months</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>3_months</t>
+          <t>6_months</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>3 Months</t>
+          <t>6 Months</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>6_months</t>
+          <t>12_months</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>6 Months</t>
+          <t>12 Months</t>
         </is>
       </c>
     </row>
@@ -1777,29 +1777,29 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>12_months</t>
+          <t>24_months</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>12 Months</t>
+          <t>24 Months</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>custom_plan_duration_choices</t>
+          <t>contact_method_2_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>24_months</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>24 Months</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1811,12 +1811,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1828,29 +1828,29 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>live_chat</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Live Chat</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>contact_method_2_choices</t>
+          <t>website_type_2_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>live_chat</t>
+          <t>wordpress</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Live Chat</t>
+          <t>WordPress</t>
         </is>
       </c>
     </row>
@@ -1862,12 +1862,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>wordpress</t>
+          <t>html</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>WordPress</t>
+          <t>HTML</t>
         </is>
       </c>
     </row>
@@ -1879,12 +1879,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>html</t>
+          <t>php</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>HTML</t>
+          <t>PHP</t>
         </is>
       </c>
     </row>
@@ -1896,27 +1896,10 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>php</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
-        <is>
-          <t>PHP</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>website_type_2_choices</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
